--- a/graphy/results/graphy_20260512_특수관계자거래.xlsx
+++ b/graphy/results/graphy_20260512_특수관계자거래.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <calcPr calcId="171027"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="결과없음" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -39,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -132,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -167,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -202,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -333,46 +402,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>검색 결과가 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(GRAPHY SMA, INC 거래처의 상품매출액/제품매출액/기타매출액 검색 결과 0건)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/graphy/results/graphy_20260512_특수관계자거래.xlsx
+++ b/graphy/results/graphy_20260512_특수관계자거래.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="결과없음" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="특수관계자거래" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,21 +427,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>검색 결과가 없습니다.</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>적요란</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>대변</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(GRAPHY SMA, INC 거래처의 상품매출액/제품매출액/기타매출액 검색 결과 0건)</t>
-        </is>
+          <t>제품매출액</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>월 합계</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1375045551</v>
       </c>
     </row>
   </sheetData>
